--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValtblPrtBotasset.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValtblPrtBotasset.xlsx
@@ -40,11 +40,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>资管资产科目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>系统资产对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合资产科目</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -412,12 +412,12 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
